--- a/data/nest_issues_commented/site_names_issues_FP.xlsx
+++ b/data/nest_issues_commented/site_names_issues_FP.xlsx
@@ -1,1090 +1,1083 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dbc1d404d722d11b/Hooded_Plover_data/R/hooded_plover_demography/data/nest_issues_commented/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_6A7AEFF34C6AE9DAC9D27D2720808C24B91226AB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CE2DA3D-D808-48CC-95EF-EDAC5A506114}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-4770" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="only_in_nest_data_FP" sheetId="1" r:id="rId1"/>
-    <sheet name="only_in_threat_data_FP" sheetId="2" r:id="rId2"/>
-    <sheet name="fuzzy_matches_to_consider" sheetId="3" r:id="rId3"/>
+    <sheet name="only_in_nest_data_FP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="only_in_threat_data_FP" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="fuzzy_matches_to_consider" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="352">
-  <si>
-    <t>season_site</t>
-  </si>
-  <si>
-    <t>issue</t>
-  </si>
-  <si>
-    <t>201011_Aldinga</t>
-  </si>
-  <si>
-    <t>only in threat data</t>
-  </si>
-  <si>
-    <t>201112_Aldinga</t>
-  </si>
-  <si>
-    <t>201213_Aldinga</t>
-  </si>
-  <si>
-    <t>201314_Aldinga</t>
-  </si>
-  <si>
-    <t>201415_Aldinga</t>
-  </si>
-  <si>
-    <t>201617_Aldinga</t>
-  </si>
-  <si>
-    <t>201920_Aldinga</t>
-  </si>
-  <si>
-    <t>202324_Aldinga</t>
-  </si>
-  <si>
-    <t>202425_Aldinga</t>
-  </si>
-  <si>
-    <t>201920_Aldinga Nth (Aldinga Beach Rd)</t>
-  </si>
-  <si>
-    <t>202122_Aldinga Nth (Aldinga Beach Rd)</t>
-  </si>
-  <si>
-    <t>202223_Aldinga Nth (Aldinga Beach Rd)</t>
-  </si>
-  <si>
-    <t>202425_Aldinga Nth (Aldinga Beach Rd)</t>
-  </si>
-  <si>
-    <t>202425_Aldinga South</t>
-  </si>
-  <si>
-    <t>202223_Aldinga Sth</t>
-  </si>
-  <si>
-    <t>202324_Aldinga Sth</t>
-  </si>
-  <si>
-    <t>201617_Aldinga Sth/Silver Sands</t>
-  </si>
-  <si>
-    <t>201213_Ballaparudda</t>
-  </si>
-  <si>
-    <t>201314_Ballaparudda</t>
-  </si>
-  <si>
-    <t>201516_Ballaparudda</t>
-  </si>
-  <si>
-    <t>201617_Ballaparudda</t>
-  </si>
-  <si>
-    <t>201718_Ballaparudda</t>
-  </si>
-  <si>
-    <t>201819_Ballaparudda</t>
-  </si>
-  <si>
-    <t>202425_Ballaparudda</t>
-  </si>
-  <si>
-    <t>201213_Bashams Beach</t>
-  </si>
-  <si>
-    <t>201314_Bashams Beach</t>
-  </si>
-  <si>
-    <t>201617_Bashams Beach</t>
-  </si>
-  <si>
-    <t>202425_Bashams Beach</t>
-  </si>
-  <si>
-    <t>201213_Callawonga</t>
-  </si>
-  <si>
-    <t>201415_Callawonga</t>
-  </si>
-  <si>
-    <t>201516_Callawonga</t>
-  </si>
-  <si>
-    <t>201617_Callawonga</t>
-  </si>
-  <si>
-    <t>201819_Callawonga</t>
-  </si>
-  <si>
-    <t>202122_Callawonga</t>
-  </si>
-  <si>
-    <t>202324_Callawonga</t>
-  </si>
-  <si>
-    <t>202425_Callawonga</t>
-  </si>
-  <si>
-    <t>200910_Carrickalinga Estuary</t>
-  </si>
-  <si>
-    <t>201011_Carrickalinga Estuary</t>
-  </si>
-  <si>
-    <t>201112_Carrickalinga Estuary</t>
-  </si>
-  <si>
-    <t>201415_Carrickalinga Estuary</t>
-  </si>
-  <si>
-    <t>201718_Carrickalinga Estuary</t>
-  </si>
-  <si>
-    <t>201920_Carrickalinga Estuary</t>
-  </si>
-  <si>
-    <t>202021_Carrickalinga Estuary</t>
-  </si>
-  <si>
-    <t>202122_Carrickalinga Estuary</t>
-  </si>
-  <si>
-    <t>202425_Carrickalinga Estuary</t>
-  </si>
-  <si>
-    <t>200910_Carrickalinga North</t>
-  </si>
-  <si>
-    <t>201213_Carrickalinga North</t>
-  </si>
-  <si>
-    <t>201314_Carrickalinga North</t>
-  </si>
-  <si>
-    <t>201415_Carrickalinga North</t>
-  </si>
-  <si>
-    <t>202425_Carrickalinga North</t>
-  </si>
-  <si>
-    <t>200910_Carrickalinga Rotunda</t>
-  </si>
-  <si>
-    <t>201112_Carrickalinga Rotunda</t>
-  </si>
-  <si>
-    <t>201617_Carrickalinga Rotunda</t>
-  </si>
-  <si>
-    <t>202425_Carrickalinga Rotunda</t>
-  </si>
-  <si>
-    <t>202425_Carrickalinga Sands (South)</t>
-  </si>
-  <si>
-    <t>201617_Carrickalinga South</t>
-  </si>
-  <si>
-    <t>201718_Carrickalinga South</t>
-  </si>
-  <si>
-    <t>201920_Carrickalinga South</t>
-  </si>
-  <si>
-    <t>202021_Carrickalinga South</t>
-  </si>
-  <si>
-    <t>202122_Carrickalinga South</t>
-  </si>
-  <si>
-    <t>202223_Carrickalinga South</t>
-  </si>
-  <si>
-    <t>202324_Carrickalinga South</t>
-  </si>
-  <si>
-    <t>201112_Christies Beach</t>
-  </si>
-  <si>
-    <t>201213_Christies Beach</t>
-  </si>
-  <si>
-    <t>201516_Christies Beach</t>
-  </si>
-  <si>
-    <t>201617_Christies Beach</t>
-  </si>
-  <si>
-    <t>201718_Christies Beach</t>
-  </si>
-  <si>
-    <t>202425_Christies Beach</t>
-  </si>
-  <si>
-    <t>200910_Coolawang</t>
-  </si>
-  <si>
-    <t>201011_Coolawang</t>
-  </si>
-  <si>
-    <t>201112_Coolawang</t>
-  </si>
-  <si>
-    <t>201314_Coolawang</t>
-  </si>
-  <si>
-    <t>201415_Coolawang</t>
-  </si>
-  <si>
-    <t>201516_Coolawang</t>
-  </si>
-  <si>
-    <t>201617_Coolawang</t>
-  </si>
-  <si>
-    <t>201920_Coolawang</t>
-  </si>
-  <si>
-    <t>202021_Coolawang</t>
-  </si>
-  <si>
-    <t>202122_Coolawang</t>
-  </si>
-  <si>
-    <t>202223_Coolawang</t>
-  </si>
-  <si>
-    <t>202425_Coolawang</t>
-  </si>
-  <si>
-    <t>201718_Deep Creek CP Blowhole beach</t>
-  </si>
-  <si>
-    <t>202324_Deep Creek CP Blowhole beach</t>
-  </si>
-  <si>
-    <t>201011_Goolwa Beach</t>
-  </si>
-  <si>
-    <t>201516_Goolwa beach</t>
-  </si>
-  <si>
-    <t>201617_Goolwa beach</t>
-  </si>
-  <si>
-    <t>201718_Goolwa beach</t>
-  </si>
-  <si>
-    <t>201819_Goolwa beach</t>
-  </si>
-  <si>
-    <t>201920_Goolwa beach</t>
-  </si>
-  <si>
-    <t>202122_Goolwa beach</t>
-  </si>
-  <si>
-    <t>202021_Hallett Cove</t>
-  </si>
-  <si>
-    <t>202122_Hallett Cove</t>
-  </si>
-  <si>
-    <t>202223_Hallett Cove</t>
-  </si>
-  <si>
-    <t>200910_Hindmarsh River Mouth</t>
-  </si>
-  <si>
-    <t>201112_Hindmarsh River Mouth</t>
-  </si>
-  <si>
-    <t>201314_Hindmarsh River Mouth</t>
-  </si>
-  <si>
-    <t>201516_Hindmarsh River Mouth</t>
-  </si>
-  <si>
-    <t>201718_Hindmarsh River Mouth</t>
-  </si>
-  <si>
-    <t>201819_Hindmarsh River Mouth</t>
-  </si>
-  <si>
-    <t>202223_Hindmarsh River Mouth</t>
-  </si>
-  <si>
-    <t>202324_Hindmarsh River Mouth</t>
-  </si>
-  <si>
-    <t>202425_Hindmarsh River Mouth</t>
-  </si>
-  <si>
-    <t>201415_Inman River Outlet</t>
-  </si>
-  <si>
-    <t>201516_Inman River Outlet</t>
-  </si>
-  <si>
-    <t>202021_Inman River Outlet</t>
-  </si>
-  <si>
-    <t>202425_Inman River Outlet</t>
-  </si>
-  <si>
-    <t>201011_Lands End</t>
-  </si>
-  <si>
-    <t>201112_Lands End</t>
-  </si>
-  <si>
-    <t>201213_Lands End</t>
-  </si>
-  <si>
-    <t>201314_Lands End</t>
-  </si>
-  <si>
-    <t>201415_Lands End</t>
-  </si>
-  <si>
-    <t>201617_Lands End</t>
-  </si>
-  <si>
-    <t>201718_Lands End</t>
-  </si>
-  <si>
-    <t>201819_Lands End</t>
-  </si>
-  <si>
-    <t>201920_Lands End</t>
-  </si>
-  <si>
-    <t>202021_Lands End</t>
-  </si>
-  <si>
-    <t>202122_Lands End</t>
-  </si>
-  <si>
-    <t>202223_Lands End</t>
-  </si>
-  <si>
-    <t>202324_Lands End</t>
-  </si>
-  <si>
-    <t>202425_Lands End</t>
-  </si>
-  <si>
-    <t>201920_Marino</t>
-  </si>
-  <si>
-    <t>202021_Marino</t>
-  </si>
-  <si>
-    <t>202021_Marino Rocks</t>
-  </si>
-  <si>
-    <t>202122_Marino Rocks</t>
-  </si>
-  <si>
-    <t>201415_Maslin Beach</t>
-  </si>
-  <si>
-    <t>201516_Maslin Beach</t>
-  </si>
-  <si>
-    <t>201617_Maslin Beach</t>
-  </si>
-  <si>
-    <t>201718_Maslin Beach</t>
-  </si>
-  <si>
-    <t>202425_Maslin Beach</t>
-  </si>
-  <si>
-    <t>202425_Maslin Beach - North</t>
-  </si>
-  <si>
-    <t>201011_Middleton Beach</t>
-  </si>
-  <si>
-    <t>201112_Middleton Beach</t>
-  </si>
-  <si>
-    <t>201213_Middleton Beach</t>
-  </si>
-  <si>
-    <t>201314_Middleton Beach</t>
-  </si>
-  <si>
-    <t>201516_Middleton Beach</t>
-  </si>
-  <si>
-    <t>202425_Middleton Beach East</t>
-  </si>
-  <si>
-    <t>202223_Middleton Beach West</t>
-  </si>
-  <si>
-    <t>202324_Middleton Beach West</t>
-  </si>
-  <si>
-    <t>202425_Middleton Beach West</t>
-  </si>
-  <si>
-    <t>201011_Moana Beach</t>
-  </si>
-  <si>
-    <t>201112_Moana Beach</t>
-  </si>
-  <si>
-    <t>201213_Moana Beach</t>
-  </si>
-  <si>
-    <t>201314_Moana Beach</t>
-  </si>
-  <si>
-    <t>201415_Moana Beach</t>
-  </si>
-  <si>
-    <t>201516_Moana Beach</t>
-  </si>
-  <si>
-    <t>201617_Moana Beach</t>
-  </si>
-  <si>
-    <t>201718_Moana Beach</t>
-  </si>
-  <si>
-    <t>202324_Moana Beach</t>
-  </si>
-  <si>
-    <t>202425_Moana Beach</t>
-  </si>
-  <si>
-    <t>201617_Moana Beach South</t>
-  </si>
-  <si>
-    <t>201718_Moana Beach South</t>
-  </si>
-  <si>
-    <t>201920_Moana Beach South</t>
-  </si>
-  <si>
-    <t>202021_Moana Beach South</t>
-  </si>
-  <si>
-    <t>202425_Moana Beach South</t>
-  </si>
-  <si>
-    <t>202021_Moana beach</t>
-  </si>
-  <si>
-    <t>200910_Morgans Beach</t>
-  </si>
-  <si>
-    <t>201011_Morgans Beach</t>
-  </si>
-  <si>
-    <t>201112_Morgans Beach</t>
-  </si>
-  <si>
-    <t>201213_Morgans Beach</t>
-  </si>
-  <si>
-    <t>201314_Morgans Beach</t>
-  </si>
-  <si>
-    <t>201415_Morgans Beach</t>
-  </si>
-  <si>
-    <t>201516_Morgans Beach</t>
-  </si>
-  <si>
-    <t>201617_Morgans Beach</t>
-  </si>
-  <si>
-    <t>201718_Morgans Beach</t>
-  </si>
-  <si>
-    <t>201920_Morgans Beach</t>
-  </si>
-  <si>
-    <t>202021_Morgans Beach</t>
-  </si>
-  <si>
-    <t>202122_Morgans Beach</t>
-  </si>
-  <si>
-    <t>202425_Morgans beach Fleurieu</t>
-  </si>
-  <si>
-    <t>201112_Myponga Beach</t>
-  </si>
-  <si>
-    <t>201213_Myponga Beach</t>
-  </si>
-  <si>
-    <t>201617_Myponga Beach</t>
-  </si>
-  <si>
-    <t>202122_Myponga Beach East</t>
-  </si>
-  <si>
-    <t>202223_Myponga Beach East</t>
-  </si>
-  <si>
-    <t>202324_Myponga Beach East</t>
-  </si>
-  <si>
-    <t>202425_Myponga Beach East</t>
-  </si>
-  <si>
-    <t>202425_Myponga Beach Estuary</t>
-  </si>
-  <si>
-    <t>202425_Normanville Estuary</t>
-  </si>
-  <si>
-    <t>200910_Normanville North</t>
-  </si>
-  <si>
-    <t>201112_Normanville North</t>
-  </si>
-  <si>
-    <t>201213_Normanville North</t>
-  </si>
-  <si>
-    <t>201415_Normanville North</t>
-  </si>
-  <si>
-    <t>201516_Normanville North</t>
-  </si>
-  <si>
-    <t>201617_Normanville North</t>
-  </si>
-  <si>
-    <t>201718_Normanville North</t>
-  </si>
-  <si>
-    <t>201920_Normanville North</t>
-  </si>
-  <si>
-    <t>202021_Normanville North</t>
-  </si>
-  <si>
-    <t>202122_Normanville North</t>
-  </si>
-  <si>
-    <t>202223_Normanville North</t>
-  </si>
-  <si>
-    <t>202324_Normanville North</t>
-  </si>
-  <si>
-    <t>202425_Normanville North</t>
-  </si>
-  <si>
-    <t>201011_Normanville South</t>
-  </si>
-  <si>
-    <t>201112_Normanville South</t>
-  </si>
-  <si>
-    <t>201213_Normanville South</t>
-  </si>
-  <si>
-    <t>201314_Normanville South</t>
-  </si>
-  <si>
-    <t>201415_Normanville South</t>
-  </si>
-  <si>
-    <t>202122_North Haven Cooroyba Court - Taperoo Gedville Road</t>
-  </si>
-  <si>
-    <t>201112_OSullivans Beach</t>
-  </si>
-  <si>
-    <t>201213_OSullivans Beach</t>
-  </si>
-  <si>
-    <t>201516_OSullivans Beach</t>
-  </si>
-  <si>
-    <t>201617_OSullivans Beach</t>
-  </si>
-  <si>
-    <t>201718_OSullivans Beach</t>
-  </si>
-  <si>
-    <t>202425_Ochre Cove, Maslins</t>
-  </si>
-  <si>
-    <t>201415_Olivers Reef</t>
-  </si>
-  <si>
-    <t>202122_Olivers Reef</t>
-  </si>
-  <si>
-    <t>202223_Olivers Reef</t>
-  </si>
-  <si>
-    <t>202324_Olivers Reef</t>
-  </si>
-  <si>
-    <t>202425_Olivers Reef</t>
-  </si>
-  <si>
-    <t>201011_Parsons Beach</t>
-  </si>
-  <si>
-    <t>201112_Parsons Beach</t>
-  </si>
-  <si>
-    <t>201213_Parsons Beach</t>
-  </si>
-  <si>
-    <t>201415_Parsons Beach</t>
-  </si>
-  <si>
-    <t>201718_Parsons Beach</t>
-  </si>
-  <si>
-    <t>202021_Parsons Beach</t>
-  </si>
-  <si>
-    <t>202122_Parsons Beach</t>
-  </si>
-  <si>
-    <t>202425_Parsons Beach</t>
-  </si>
-  <si>
-    <t>201213_Port Stanvac</t>
-  </si>
-  <si>
-    <t>201516_Port Stanvac</t>
-  </si>
-  <si>
-    <t>202122_Port Stanvac</t>
-  </si>
-  <si>
-    <t>202425_Port Stanvac</t>
-  </si>
-  <si>
-    <t>201415_Port Willunga</t>
-  </si>
-  <si>
-    <t>202425_Port Willunga</t>
-  </si>
-  <si>
-    <t>202425_Port Willunga - Chinaman Gully</t>
-  </si>
-  <si>
-    <t>202425_Port Willunga South</t>
-  </si>
-  <si>
-    <t>202324_Sellicks Beach</t>
-  </si>
-  <si>
-    <t>202425_Sellicks Beach</t>
-  </si>
-  <si>
-    <t>202122_Semaphore Park (Mirani Ct - Recreation Pde)</t>
-  </si>
-  <si>
-    <t>202122_Semaphore Sth (Recreation Pde - Bower Rd)</t>
-  </si>
-  <si>
-    <t>201112_Sheepies beach</t>
-  </si>
-  <si>
-    <t>201213_Sheepies beach</t>
-  </si>
-  <si>
-    <t>201314_Sheepies beach</t>
-  </si>
-  <si>
-    <t>201516_Sheepies beach</t>
-  </si>
-  <si>
-    <t>201617_Sheepies beach</t>
-  </si>
-  <si>
-    <t>202425_Sheepies beach</t>
-  </si>
-  <si>
-    <t>201314_Shelley Beach (lady bay)</t>
-  </si>
-  <si>
-    <t>201516_Shelley Beach (lady bay)</t>
-  </si>
-  <si>
-    <t>201718_Shelley Beach (lady bay)</t>
-  </si>
-  <si>
-    <t>202425_Shelley Beach (lady bay)</t>
-  </si>
-  <si>
-    <t>201011_Silver Sands</t>
-  </si>
-  <si>
-    <t>201112_Silver Sands</t>
-  </si>
-  <si>
-    <t>201415_Silver Sands</t>
-  </si>
-  <si>
-    <t>201718_Silver Sands</t>
-  </si>
-  <si>
-    <t>201920_Silver Sands</t>
-  </si>
-  <si>
-    <t>202021_Silver Sands</t>
-  </si>
-  <si>
-    <t>202223_Silver Sands</t>
-  </si>
-  <si>
-    <t>202324_Silver Sands</t>
-  </si>
-  <si>
-    <t>202425_Silver Sands</t>
-  </si>
-  <si>
-    <t>201314_Snapper Point</t>
-  </si>
-  <si>
-    <t>201415_Snapper Point</t>
-  </si>
-  <si>
-    <t>201718_Snapper Point</t>
-  </si>
-  <si>
-    <t>202021_Snapper Point</t>
-  </si>
-  <si>
-    <t>202122_Snapper Point</t>
-  </si>
-  <si>
-    <t>202223_Snapper Point</t>
-  </si>
-  <si>
-    <t>202425_Snapper Point</t>
-  </si>
-  <si>
-    <t>202425_Snapper Point North</t>
-  </si>
-  <si>
-    <t>201011_Southport</t>
-  </si>
-  <si>
-    <t>201213_Southport</t>
-  </si>
-  <si>
-    <t>201314_Southport</t>
-  </si>
-  <si>
-    <t>201415_Southport</t>
-  </si>
-  <si>
-    <t>201516_Southport</t>
-  </si>
-  <si>
-    <t>201617_Southport</t>
-  </si>
-  <si>
-    <t>201718_Southport</t>
-  </si>
-  <si>
-    <t>201920_Southport</t>
-  </si>
-  <si>
-    <t>202021_Southport</t>
-  </si>
-  <si>
-    <t>202122_Southport</t>
-  </si>
-  <si>
-    <t>202223_Southport</t>
-  </si>
-  <si>
-    <t>202425_Southport</t>
-  </si>
-  <si>
-    <t>202021_Tennyson Beach</t>
-  </si>
-  <si>
-    <t>201920_Tennyson Dunes</t>
-  </si>
-  <si>
-    <t>202021_Tennyson Dunes (Estcourt Rd Fort St)</t>
-  </si>
-  <si>
-    <t>202122_Tennyson Dunes (Estcourt Rd Fort St)</t>
-  </si>
-  <si>
-    <t>202425_Tokuremoar West</t>
-  </si>
-  <si>
-    <t>202324_Trig point</t>
-  </si>
-  <si>
-    <t>202425_Trig point</t>
-  </si>
-  <si>
-    <t>201617_Tunkalilla 1st alcove far east</t>
-  </si>
-  <si>
-    <t>201718_Tunkalilla 1st alcove far east</t>
-  </si>
-  <si>
-    <t>201819_Tunkalilla 1st alcove far east</t>
-  </si>
-  <si>
-    <t>201920_Tunkalilla 1st alcove far east</t>
-  </si>
-  <si>
-    <t>202021_Tunkalilla 1st alcove far east</t>
-  </si>
-  <si>
-    <t>202122_Tunkalilla 1st alcove far east</t>
-  </si>
-  <si>
-    <t>202223_Tunkalilla 1st alcove far east</t>
-  </si>
-  <si>
-    <t>202324_Tunkalilla 1st alcove far east</t>
-  </si>
-  <si>
-    <t>202425_Tunkalilla 1st alcove far east</t>
-  </si>
-  <si>
-    <t>201314_Tunkalilla East</t>
-  </si>
-  <si>
-    <t>201819_Tunkalilla East</t>
-  </si>
-  <si>
-    <t>202425_Tunkalilla East</t>
-  </si>
-  <si>
-    <t>201415_Tunkalilla Inner West</t>
-  </si>
-  <si>
-    <t>201516_Tunkalilla Inner West</t>
-  </si>
-  <si>
-    <t>201718_Tunkalilla Inner West</t>
-  </si>
-  <si>
-    <t>201819_Tunkalilla Inner West</t>
-  </si>
-  <si>
-    <t>202425_Tunkalilla Inner West</t>
-  </si>
-  <si>
-    <t>201011_Tunkalilla Midway</t>
-  </si>
-  <si>
-    <t>201112_Tunkalilla Midway</t>
-  </si>
-  <si>
-    <t>201213_Tunkalilla Midway</t>
-  </si>
-  <si>
-    <t>201314_Tunkalilla Midway</t>
-  </si>
-  <si>
-    <t>201415_Tunkalilla Midway</t>
-  </si>
-  <si>
-    <t>201516_Tunkalilla Midway</t>
-  </si>
-  <si>
-    <t>201617_Tunkalilla Midway</t>
-  </si>
-  <si>
-    <t>201718_Tunkalilla Midway</t>
-  </si>
-  <si>
-    <t>202425_Tunkalilla Midway</t>
-  </si>
-  <si>
-    <t>201617_Tunkalilla Tunk Head alcove</t>
-  </si>
-  <si>
-    <t>201718_Tunkalilla Tunk Head alcove</t>
-  </si>
-  <si>
-    <t>201920_Tunkalilla Tunk Head alcove</t>
-  </si>
-  <si>
-    <t>202021_Tunkalilla Tunk Head alcove</t>
-  </si>
-  <si>
-    <t>202122_Tunkalilla Tunk Head alcove</t>
-  </si>
-  <si>
-    <t>201112_Tunkalilla West</t>
-  </si>
-  <si>
-    <t>201516_Tunkalilla West</t>
-  </si>
-  <si>
-    <t>201718_Tunkalilla West</t>
-  </si>
-  <si>
-    <t>201819_Tunkalilla West</t>
-  </si>
-  <si>
-    <t>202425_Tunkalilla West</t>
-  </si>
-  <si>
-    <t>202021_Victor Central</t>
-  </si>
-  <si>
-    <t>202425_Victor Central</t>
-  </si>
-  <si>
-    <t>201011_Waitpinga Beach</t>
-  </si>
-  <si>
-    <t>201314_Waitpinga Beach</t>
-  </si>
-  <si>
-    <t>201112_Waitpinga Beach (east)</t>
-  </si>
-  <si>
-    <t>201415_Waitpinga Beach (east)</t>
-  </si>
-  <si>
-    <t>202425_Waitpinga Beach (east)</t>
-  </si>
-  <si>
-    <t>201516_Waitpinga Beach (west)</t>
-  </si>
-  <si>
-    <t>201617_Waitpinga Beach (west)</t>
-  </si>
-  <si>
-    <t>201718_Waitpinga Beach (west)</t>
-  </si>
-  <si>
-    <t>201819_Waitpinga Beach (west)</t>
-  </si>
-  <si>
-    <t>201920_Waitpinga Beach (west)</t>
-  </si>
-  <si>
-    <t>202223_Waitpinga Beach (west)</t>
-  </si>
-  <si>
-    <t>202425_Waitpinga Beach (west)</t>
-  </si>
-  <si>
-    <t>201617_Waitpinga Estuary</t>
-  </si>
-  <si>
-    <t>201718_Waitpinga Estuary</t>
-  </si>
-  <si>
-    <t>201819_Waitpinga Estuary</t>
-  </si>
-  <si>
-    <t>201920_Waitpinga Estuary</t>
-  </si>
-  <si>
-    <t>202122_Waitpinga Estuary</t>
-  </si>
-  <si>
-    <t>202223_Waitpinga Estuary</t>
-  </si>
-  <si>
-    <t>202324_Waitpinga Estuary</t>
-  </si>
-  <si>
-    <t>202425_Waitpinga Estuary</t>
-  </si>
-  <si>
-    <t>201112_Watsons Gap</t>
-  </si>
-  <si>
-    <t>201415_Watsons Gap</t>
-  </si>
-  <si>
-    <t>202425_Watsons Gap</t>
-  </si>
-  <si>
-    <t>202425_Wattle steps</t>
-  </si>
-  <si>
-    <t>202021_West Lakes Beach (Estcourt Rd - Mirani Ct)</t>
-  </si>
-  <si>
-    <t>202122_West Lakes Beach (Estcourt Rd - Mirani Ct)</t>
-  </si>
-  <si>
-    <t>202425_Whalers</t>
-  </si>
-  <si>
-    <t>201314_Yankalilla river mouth</t>
-  </si>
-  <si>
-    <t>201516_Yankalilla river mouth</t>
-  </si>
-  <si>
-    <t>201617_Yankalilla river mouth</t>
-  </si>
-  <si>
-    <t>201718_Yankalilla river mouth</t>
-  </si>
-  <si>
-    <t>202021_Yankalilla river mouth</t>
-  </si>
-  <si>
-    <t>202122_Yankalilla river mouth</t>
-  </si>
-  <si>
-    <t>202425_Yankalilla river mouth</t>
-  </si>
-  <si>
-    <t>202425_Yilki</t>
-  </si>
-  <si>
-    <t>season</t>
-  </si>
-  <si>
-    <t>site_nest_data</t>
-  </si>
-  <si>
-    <t>site_threat_data</t>
-  </si>
-  <si>
-    <t>dist</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="352">
+  <si>
+    <t xml:space="preserve">season_site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">issue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201011_Aldinga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">only in threat data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201112_Aldinga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201213_Aldinga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201314_Aldinga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201415_Aldinga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201617_Aldinga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201920_Aldinga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202324_Aldinga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Aldinga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201920_Aldinga Nth (Aldinga Beach Rd)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202122_Aldinga Nth (Aldinga Beach Rd)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202223_Aldinga Nth (Aldinga Beach Rd)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Aldinga Nth (Aldinga Beach Rd)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Aldinga South</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202223_Aldinga Sth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202324_Aldinga Sth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201617_Aldinga Sth/Silver Sands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201213_Ballaparudda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201314_Ballaparudda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201516_Ballaparudda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201617_Ballaparudda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201718_Ballaparudda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201819_Ballaparudda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Ballaparudda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201213_Bashams Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201314_Bashams Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201617_Bashams Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Bashams Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201213_Callawonga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201415_Callawonga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201516_Callawonga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201617_Callawonga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201819_Callawonga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202122_Callawonga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202324_Callawonga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Callawonga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200910_Carrickalinga Estuary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201011_Carrickalinga Estuary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201112_Carrickalinga Estuary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201415_Carrickalinga Estuary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201718_Carrickalinga Estuary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201920_Carrickalinga Estuary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202021_Carrickalinga Estuary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202122_Carrickalinga Estuary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Carrickalinga Estuary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200910_Carrickalinga North</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201213_Carrickalinga North</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201314_Carrickalinga North</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201415_Carrickalinga North</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Carrickalinga North</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200910_Carrickalinga Rotunda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201112_Carrickalinga Rotunda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201617_Carrickalinga Rotunda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Carrickalinga Rotunda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Carrickalinga Sands (South)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201617_Carrickalinga South</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201718_Carrickalinga South</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201920_Carrickalinga South</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202021_Carrickalinga South</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202122_Carrickalinga South</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202223_Carrickalinga South</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202324_Carrickalinga South</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201112_Christies Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201213_Christies Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201516_Christies Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201617_Christies Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201718_Christies Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Christies Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200910_Coolawang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201011_Coolawang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201112_Coolawang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201314_Coolawang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201415_Coolawang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201516_Coolawang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201617_Coolawang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201920_Coolawang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202021_Coolawang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202122_Coolawang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202223_Coolawang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Coolawang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201718_Deep Creek CP Blowhole beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202324_Deep Creek CP Blowhole beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201011_Goolwa Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201516_Goolwa beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201617_Goolwa beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201718_Goolwa beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201819_Goolwa beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201920_Goolwa beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202122_Goolwa beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202021_Hallett Cove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202122_Hallett Cove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202223_Hallett Cove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200910_Hindmarsh River Mouth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201112_Hindmarsh River Mouth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201314_Hindmarsh River Mouth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201516_Hindmarsh River Mouth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201718_Hindmarsh River Mouth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201819_Hindmarsh River Mouth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202223_Hindmarsh River Mouth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202324_Hindmarsh River Mouth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Hindmarsh River Mouth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201415_Inman River Outlet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201516_Inman River Outlet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202021_Inman River Outlet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Inman River Outlet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201011_Lands End</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201112_Lands End</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201213_Lands End</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201314_Lands End</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201415_Lands End</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201617_Lands End</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201718_Lands End</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201819_Lands End</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201920_Lands End</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202021_Lands End</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202122_Lands End</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202223_Lands End</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202324_Lands End</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Lands End</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201920_Marino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202021_Marino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202021_Marino Rocks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202122_Marino Rocks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201415_Maslin Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201516_Maslin Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201617_Maslin Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201718_Maslin Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Maslin Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Maslin Beach - North</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201011_Middleton Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201112_Middleton Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201213_Middleton Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201314_Middleton Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201516_Middleton Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Middleton Beach East</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202223_Middleton Beach West</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202324_Middleton Beach West</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Middleton Beach West</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201011_Moana Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201112_Moana Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201213_Moana Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201314_Moana Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201415_Moana Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201516_Moana Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201617_Moana Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201718_Moana Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202324_Moana Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Moana Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201617_Moana Beach South</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201718_Moana Beach South</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201920_Moana Beach South</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202021_Moana Beach South</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Moana Beach South</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202021_Moana beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200910_Morgans Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201011_Morgans Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201112_Morgans Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201213_Morgans Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201314_Morgans Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201415_Morgans Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201516_Morgans Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201617_Morgans Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201718_Morgans Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201920_Morgans Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202021_Morgans Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202122_Morgans Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Morgans beach Fleurieu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201112_Myponga Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201213_Myponga Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201617_Myponga Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202122_Myponga Beach East</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202223_Myponga Beach East</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202324_Myponga Beach East</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Myponga Beach East</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Myponga Beach Estuary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Normanville Estuary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200910_Normanville North</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201112_Normanville North</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201213_Normanville North</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201415_Normanville North</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201516_Normanville North</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201617_Normanville North</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201718_Normanville North</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201920_Normanville North</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202021_Normanville North</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202122_Normanville North</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202223_Normanville North</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202324_Normanville North</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Normanville North</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201011_Normanville South</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201112_Normanville South</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201213_Normanville South</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201314_Normanville South</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201415_Normanville South</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202122_North Haven Cooroyba Court - Taperoo Gedville Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201112_OSullivans Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201213_OSullivans Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201516_OSullivans Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201617_OSullivans Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201718_OSullivans Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Ochre Cove, Maslins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201415_Olivers Reef</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202122_Olivers Reef</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202223_Olivers Reef</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202324_Olivers Reef</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Olivers Reef</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201011_Parsons Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201112_Parsons Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201213_Parsons Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201415_Parsons Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201718_Parsons Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202021_Parsons Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202122_Parsons Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Parsons Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201213_Port Stanvac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201516_Port Stanvac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202122_Port Stanvac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Port Stanvac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201415_Port Willunga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Port Willunga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Port Willunga - Chinaman Gully</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Port Willunga South</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202324_Sellicks Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Sellicks Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202122_Semaphore Park (Mirani Ct - Recreation Pde)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202122_Semaphore Sth (Recreation Pde - Bower Rd)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201112_Sheepies beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201213_Sheepies beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201314_Sheepies beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201516_Sheepies beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201617_Sheepies beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Sheepies beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201314_Shelley Beach (lady bay)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201516_Shelley Beach (lady bay)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201718_Shelley Beach (lady bay)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Shelley Beach (lady bay)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201011_Silver Sands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201112_Silver Sands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201415_Silver Sands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201718_Silver Sands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201920_Silver Sands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202021_Silver Sands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202223_Silver Sands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202324_Silver Sands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Silver Sands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201314_Snapper Point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201415_Snapper Point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201718_Snapper Point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202021_Snapper Point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202122_Snapper Point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202223_Snapper Point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Snapper Point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Snapper Point North</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201011_Southport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201213_Southport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201314_Southport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201415_Southport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201516_Southport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201617_Southport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201718_Southport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201920_Southport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202021_Southport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202122_Southport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202223_Southport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Southport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202021_Tennyson Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201920_Tennyson Dunes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202021_Tennyson Dunes (Estcourt Rd Fort St)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202122_Tennyson Dunes (Estcourt Rd Fort St)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Tokuremoar West</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202324_Trig point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Trig point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201617_Tunkalilla 1st alcove far east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201718_Tunkalilla 1st alcove far east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201819_Tunkalilla 1st alcove far east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201920_Tunkalilla 1st alcove far east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202021_Tunkalilla 1st alcove far east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202122_Tunkalilla 1st alcove far east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202223_Tunkalilla 1st alcove far east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202324_Tunkalilla 1st alcove far east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Tunkalilla 1st alcove far east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201314_Tunkalilla East</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201819_Tunkalilla East</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Tunkalilla East</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201415_Tunkalilla Inner West</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201516_Tunkalilla Inner West</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201718_Tunkalilla Inner West</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201819_Tunkalilla Inner West</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Tunkalilla Inner West</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201011_Tunkalilla Midway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201112_Tunkalilla Midway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201213_Tunkalilla Midway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201314_Tunkalilla Midway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201415_Tunkalilla Midway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201516_Tunkalilla Midway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201617_Tunkalilla Midway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201718_Tunkalilla Midway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Tunkalilla Midway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201617_Tunkalilla Tunk Head alcove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201718_Tunkalilla Tunk Head alcove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201920_Tunkalilla Tunk Head alcove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202021_Tunkalilla Tunk Head alcove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202122_Tunkalilla Tunk Head alcove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201112_Tunkalilla West</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201516_Tunkalilla West</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201718_Tunkalilla West</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201819_Tunkalilla West</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Tunkalilla West</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202021_Victor Central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Victor Central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201011_Waitpinga Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201314_Waitpinga Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201112_Waitpinga Beach (east)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201415_Waitpinga Beach (east)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Waitpinga Beach (east)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201516_Waitpinga Beach (west)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201617_Waitpinga Beach (west)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201718_Waitpinga Beach (west)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201819_Waitpinga Beach (west)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201920_Waitpinga Beach (west)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202223_Waitpinga Beach (west)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Waitpinga Beach (west)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201617_Waitpinga Estuary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201718_Waitpinga Estuary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201819_Waitpinga Estuary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201920_Waitpinga Estuary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202122_Waitpinga Estuary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202223_Waitpinga Estuary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202324_Waitpinga Estuary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Waitpinga Estuary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201112_Watsons Gap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201415_Watsons Gap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Watsons Gap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Wattle steps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202021_West Lakes Beach (Estcourt Rd - Mirani Ct)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202122_West Lakes Beach (Estcourt Rd - Mirani Ct)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Whalers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201314_Yankalilla river mouth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201516_Yankalilla river mouth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201617_Yankalilla river mouth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201718_Yankalilla river mouth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202021_Yankalilla river mouth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202122_Yankalilla river mouth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Yankalilla river mouth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202425_Yilki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">season</t>
+  </si>
+  <si>
+    <t xml:space="preserve">site_nest_data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">site_threat_data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dist</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1120,15 +1113,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -1410,11 +1394,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1424,19 +1408,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B346"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="56.42578125" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1444,7 +1425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1452,7 +1433,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1460,7 +1441,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1468,7 +1449,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1476,7 +1457,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1484,7 +1465,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1492,7 +1473,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1500,7 +1481,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1508,7 +1489,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1516,7 +1497,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1524,7 +1505,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -1532,7 +1513,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1540,7 +1521,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1548,7 +1529,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -1556,7 +1537,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1564,7 +1545,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -1572,7 +1553,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -1580,7 +1561,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -1588,7 +1569,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -1596,7 +1577,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -1604,7 +1585,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -1612,7 +1593,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -1620,7 +1601,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -1628,7 +1609,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -1636,7 +1617,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -1644,7 +1625,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -1652,7 +1633,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -1660,7 +1641,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -1668,7 +1649,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -1676,7 +1657,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -1684,7 +1665,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -1692,7 +1673,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33">
       <c r="A33" t="s">
         <v>34</v>
       </c>
@@ -1700,7 +1681,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34">
       <c r="A34" t="s">
         <v>35</v>
       </c>
@@ -1708,7 +1689,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35">
       <c r="A35" t="s">
         <v>36</v>
       </c>
@@ -1716,7 +1697,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36">
       <c r="A36" t="s">
         <v>37</v>
       </c>
@@ -1724,7 +1705,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37">
       <c r="A37" t="s">
         <v>38</v>
       </c>
@@ -1732,7 +1713,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38">
       <c r="A38" t="s">
         <v>39</v>
       </c>
@@ -1740,7 +1721,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39">
       <c r="A39" t="s">
         <v>40</v>
       </c>
@@ -1748,7 +1729,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40">
       <c r="A40" t="s">
         <v>41</v>
       </c>
@@ -1756,7 +1737,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41">
       <c r="A41" t="s">
         <v>42</v>
       </c>
@@ -1764,7 +1745,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42">
       <c r="A42" t="s">
         <v>43</v>
       </c>
@@ -1772,7 +1753,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43">
       <c r="A43" t="s">
         <v>44</v>
       </c>
@@ -1780,7 +1761,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44">
       <c r="A44" t="s">
         <v>45</v>
       </c>
@@ -1788,7 +1769,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45">
       <c r="A45" t="s">
         <v>46</v>
       </c>
@@ -1796,7 +1777,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46">
       <c r="A46" t="s">
         <v>47</v>
       </c>
@@ -1804,7 +1785,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47">
       <c r="A47" t="s">
         <v>48</v>
       </c>
@@ -1812,7 +1793,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48">
       <c r="A48" t="s">
         <v>49</v>
       </c>
@@ -1820,7 +1801,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49">
       <c r="A49" t="s">
         <v>50</v>
       </c>
@@ -1828,7 +1809,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50">
       <c r="A50" t="s">
         <v>51</v>
       </c>
@@ -1836,7 +1817,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51">
       <c r="A51" t="s">
         <v>52</v>
       </c>
@@ -1844,7 +1825,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52">
       <c r="A52" t="s">
         <v>53</v>
       </c>
@@ -1852,7 +1833,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53">
       <c r="A53" t="s">
         <v>54</v>
       </c>
@@ -1860,7 +1841,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54">
       <c r="A54" t="s">
         <v>55</v>
       </c>
@@ -1868,7 +1849,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55">
       <c r="A55" t="s">
         <v>56</v>
       </c>
@@ -1876,7 +1857,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56">
       <c r="A56" t="s">
         <v>57</v>
       </c>
@@ -1884,7 +1865,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57">
       <c r="A57" t="s">
         <v>58</v>
       </c>
@@ -1892,7 +1873,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58">
       <c r="A58" t="s">
         <v>59</v>
       </c>
@@ -1900,7 +1881,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59">
       <c r="A59" t="s">
         <v>60</v>
       </c>
@@ -1908,7 +1889,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60">
       <c r="A60" t="s">
         <v>61</v>
       </c>
@@ -1916,7 +1897,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61">
       <c r="A61" t="s">
         <v>62</v>
       </c>
@@ -1924,7 +1905,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62">
       <c r="A62" t="s">
         <v>63</v>
       </c>
@@ -1932,7 +1913,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63">
       <c r="A63" t="s">
         <v>64</v>
       </c>
@@ -1940,7 +1921,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64">
       <c r="A64" t="s">
         <v>65</v>
       </c>
@@ -1948,7 +1929,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65">
       <c r="A65" t="s">
         <v>66</v>
       </c>
@@ -1956,7 +1937,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66">
       <c r="A66" t="s">
         <v>67</v>
       </c>
@@ -1964,7 +1945,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67">
       <c r="A67" t="s">
         <v>68</v>
       </c>
@@ -1972,7 +1953,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68">
       <c r="A68" t="s">
         <v>69</v>
       </c>
@@ -1980,7 +1961,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69">
       <c r="A69" t="s">
         <v>70</v>
       </c>
@@ -1988,7 +1969,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70">
       <c r="A70" t="s">
         <v>71</v>
       </c>
@@ -1996,7 +1977,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71">
       <c r="A71" t="s">
         <v>72</v>
       </c>
@@ -2004,7 +1985,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72">
       <c r="A72" t="s">
         <v>73</v>
       </c>
@@ -2012,7 +1993,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73">
       <c r="A73" t="s">
         <v>74</v>
       </c>
@@ -2020,7 +2001,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74">
       <c r="A74" t="s">
         <v>75</v>
       </c>
@@ -2028,7 +2009,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75">
       <c r="A75" t="s">
         <v>76</v>
       </c>
@@ -2036,7 +2017,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76">
       <c r="A76" t="s">
         <v>77</v>
       </c>
@@ -2044,7 +2025,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77">
       <c r="A77" t="s">
         <v>78</v>
       </c>
@@ -2052,7 +2033,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78">
       <c r="A78" t="s">
         <v>79</v>
       </c>
@@ -2060,7 +2041,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79">
       <c r="A79" t="s">
         <v>80</v>
       </c>
@@ -2068,7 +2049,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80">
       <c r="A80" t="s">
         <v>81</v>
       </c>
@@ -2076,7 +2057,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81">
       <c r="A81" t="s">
         <v>82</v>
       </c>
@@ -2084,7 +2065,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82">
       <c r="A82" t="s">
         <v>83</v>
       </c>
@@ -2092,7 +2073,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83">
       <c r="A83" t="s">
         <v>84</v>
       </c>
@@ -2100,7 +2081,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84">
       <c r="A84" t="s">
         <v>85</v>
       </c>
@@ -2108,7 +2089,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85">
       <c r="A85" t="s">
         <v>86</v>
       </c>
@@ -2116,7 +2097,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86">
       <c r="A86" t="s">
         <v>87</v>
       </c>
@@ -2124,7 +2105,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87">
       <c r="A87" t="s">
         <v>88</v>
       </c>
@@ -2132,7 +2113,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88">
       <c r="A88" t="s">
         <v>89</v>
       </c>
@@ -2140,7 +2121,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89">
       <c r="A89" t="s">
         <v>90</v>
       </c>
@@ -2148,7 +2129,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90">
       <c r="A90" t="s">
         <v>91</v>
       </c>
@@ -2156,7 +2137,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91">
       <c r="A91" t="s">
         <v>92</v>
       </c>
@@ -2164,7 +2145,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92">
       <c r="A92" t="s">
         <v>93</v>
       </c>
@@ -2172,7 +2153,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93">
       <c r="A93" t="s">
         <v>94</v>
       </c>
@@ -2180,7 +2161,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94">
       <c r="A94" t="s">
         <v>95</v>
       </c>
@@ -2188,7 +2169,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95">
       <c r="A95" t="s">
         <v>96</v>
       </c>
@@ -2196,7 +2177,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96">
       <c r="A96" t="s">
         <v>97</v>
       </c>
@@ -2204,7 +2185,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97">
       <c r="A97" t="s">
         <v>98</v>
       </c>
@@ -2212,7 +2193,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="98">
       <c r="A98" t="s">
         <v>99</v>
       </c>
@@ -2220,7 +2201,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99">
       <c r="A99" t="s">
         <v>100</v>
       </c>
@@ -2228,7 +2209,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="100">
       <c r="A100" t="s">
         <v>101</v>
       </c>
@@ -2236,7 +2217,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="101">
       <c r="A101" t="s">
         <v>102</v>
       </c>
@@ -2244,7 +2225,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102">
       <c r="A102" t="s">
         <v>103</v>
       </c>
@@ -2252,7 +2233,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="103">
       <c r="A103" t="s">
         <v>104</v>
       </c>
@@ -2260,7 +2241,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="104">
       <c r="A104" t="s">
         <v>105</v>
       </c>
@@ -2268,7 +2249,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="105">
       <c r="A105" t="s">
         <v>106</v>
       </c>
@@ -2276,7 +2257,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="106">
       <c r="A106" t="s">
         <v>107</v>
       </c>
@@ -2284,7 +2265,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="107">
       <c r="A107" t="s">
         <v>108</v>
       </c>
@@ -2292,7 +2273,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="108">
       <c r="A108" t="s">
         <v>109</v>
       </c>
@@ -2300,7 +2281,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="109">
       <c r="A109" t="s">
         <v>110</v>
       </c>
@@ -2308,7 +2289,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="110">
       <c r="A110" t="s">
         <v>111</v>
       </c>
@@ -2316,7 +2297,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="111">
       <c r="A111" t="s">
         <v>112</v>
       </c>
@@ -2324,7 +2305,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="112">
       <c r="A112" t="s">
         <v>113</v>
       </c>
@@ -2332,7 +2313,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="113">
       <c r="A113" t="s">
         <v>114</v>
       </c>
@@ -2340,7 +2321,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="114">
       <c r="A114" t="s">
         <v>115</v>
       </c>
@@ -2348,7 +2329,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="115">
       <c r="A115" t="s">
         <v>116</v>
       </c>
@@ -2356,7 +2337,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="116">
       <c r="A116" t="s">
         <v>117</v>
       </c>
@@ -2364,7 +2345,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="117">
       <c r="A117" t="s">
         <v>118</v>
       </c>
@@ -2372,7 +2353,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="118">
       <c r="A118" t="s">
         <v>119</v>
       </c>
@@ -2380,7 +2361,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="119">
       <c r="A119" t="s">
         <v>120</v>
       </c>
@@ -2388,7 +2369,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="120">
       <c r="A120" t="s">
         <v>121</v>
       </c>
@@ -2396,7 +2377,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="121">
       <c r="A121" t="s">
         <v>122</v>
       </c>
@@ -2404,7 +2385,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="122">
       <c r="A122" t="s">
         <v>123</v>
       </c>
@@ -2412,7 +2393,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="123">
       <c r="A123" t="s">
         <v>124</v>
       </c>
@@ -2420,7 +2401,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="124">
       <c r="A124" t="s">
         <v>125</v>
       </c>
@@ -2428,7 +2409,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="125">
       <c r="A125" t="s">
         <v>126</v>
       </c>
@@ -2436,7 +2417,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="126">
       <c r="A126" t="s">
         <v>127</v>
       </c>
@@ -2444,7 +2425,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="127">
       <c r="A127" t="s">
         <v>128</v>
       </c>
@@ -2452,7 +2433,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="128">
       <c r="A128" t="s">
         <v>129</v>
       </c>
@@ -2460,7 +2441,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="129">
       <c r="A129" t="s">
         <v>130</v>
       </c>
@@ -2468,7 +2449,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="130">
       <c r="A130" t="s">
         <v>131</v>
       </c>
@@ -2476,7 +2457,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="131">
       <c r="A131" t="s">
         <v>132</v>
       </c>
@@ -2484,7 +2465,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="132">
       <c r="A132" t="s">
         <v>133</v>
       </c>
@@ -2492,7 +2473,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="133">
       <c r="A133" t="s">
         <v>134</v>
       </c>
@@ -2500,7 +2481,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="134">
       <c r="A134" t="s">
         <v>135</v>
       </c>
@@ -2508,7 +2489,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="135">
       <c r="A135" t="s">
         <v>136</v>
       </c>
@@ -2516,7 +2497,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="136">
       <c r="A136" t="s">
         <v>137</v>
       </c>
@@ -2524,7 +2505,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="137">
       <c r="A137" t="s">
         <v>138</v>
       </c>
@@ -2532,7 +2513,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="138">
       <c r="A138" t="s">
         <v>139</v>
       </c>
@@ -2540,7 +2521,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="139">
       <c r="A139" t="s">
         <v>140</v>
       </c>
@@ -2548,7 +2529,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="140">
       <c r="A140" t="s">
         <v>141</v>
       </c>
@@ -2556,7 +2537,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="141">
       <c r="A141" t="s">
         <v>142</v>
       </c>
@@ -2564,7 +2545,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="142">
       <c r="A142" t="s">
         <v>143</v>
       </c>
@@ -2572,7 +2553,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="143">
       <c r="A143" t="s">
         <v>144</v>
       </c>
@@ -2580,7 +2561,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="144">
       <c r="A144" t="s">
         <v>145</v>
       </c>
@@ -2588,7 +2569,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="145">
       <c r="A145" t="s">
         <v>146</v>
       </c>
@@ -2596,7 +2577,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="146">
       <c r="A146" t="s">
         <v>147</v>
       </c>
@@ -2604,7 +2585,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="147">
       <c r="A147" t="s">
         <v>148</v>
       </c>
@@ -2612,7 +2593,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="148">
       <c r="A148" t="s">
         <v>149</v>
       </c>
@@ -2620,7 +2601,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="149">
       <c r="A149" t="s">
         <v>150</v>
       </c>
@@ -2628,7 +2609,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="150">
       <c r="A150" t="s">
         <v>151</v>
       </c>
@@ -2636,7 +2617,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="151">
       <c r="A151" t="s">
         <v>152</v>
       </c>
@@ -2644,7 +2625,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="152">
       <c r="A152" t="s">
         <v>153</v>
       </c>
@@ -2652,7 +2633,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="153">
       <c r="A153" t="s">
         <v>154</v>
       </c>
@@ -2660,7 +2641,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="154">
       <c r="A154" t="s">
         <v>155</v>
       </c>
@@ -2668,7 +2649,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="155">
       <c r="A155" t="s">
         <v>156</v>
       </c>
@@ -2676,7 +2657,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="156">
       <c r="A156" t="s">
         <v>157</v>
       </c>
@@ -2684,7 +2665,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="157">
       <c r="A157" t="s">
         <v>158</v>
       </c>
@@ -2692,7 +2673,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="158">
       <c r="A158" t="s">
         <v>159</v>
       </c>
@@ -2700,7 +2681,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="159">
       <c r="A159" t="s">
         <v>160</v>
       </c>
@@ -2708,7 +2689,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="160">
       <c r="A160" t="s">
         <v>161</v>
       </c>
@@ -2716,7 +2697,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="161">
       <c r="A161" t="s">
         <v>162</v>
       </c>
@@ -2724,7 +2705,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="162">
       <c r="A162" t="s">
         <v>163</v>
       </c>
@@ -2732,7 +2713,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="163">
       <c r="A163" t="s">
         <v>164</v>
       </c>
@@ -2740,7 +2721,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="164">
       <c r="A164" t="s">
         <v>165</v>
       </c>
@@ -2748,7 +2729,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="165">
       <c r="A165" t="s">
         <v>166</v>
       </c>
@@ -2756,7 +2737,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="166">
       <c r="A166" t="s">
         <v>167</v>
       </c>
@@ -2764,7 +2745,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="167">
       <c r="A167" t="s">
         <v>168</v>
       </c>
@@ -2772,7 +2753,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="168">
       <c r="A168" t="s">
         <v>169</v>
       </c>
@@ -2780,7 +2761,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="169">
       <c r="A169" t="s">
         <v>170</v>
       </c>
@@ -2788,7 +2769,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="170">
       <c r="A170" t="s">
         <v>171</v>
       </c>
@@ -2796,7 +2777,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="171">
       <c r="A171" t="s">
         <v>172</v>
       </c>
@@ -2804,7 +2785,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="172">
       <c r="A172" t="s">
         <v>173</v>
       </c>
@@ -2812,7 +2793,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="173">
       <c r="A173" t="s">
         <v>174</v>
       </c>
@@ -2820,7 +2801,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="174">
       <c r="A174" t="s">
         <v>175</v>
       </c>
@@ -2828,7 +2809,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="175">
       <c r="A175" t="s">
         <v>176</v>
       </c>
@@ -2836,7 +2817,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="176">
       <c r="A176" t="s">
         <v>177</v>
       </c>
@@ -2844,7 +2825,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="177">
       <c r="A177" t="s">
         <v>178</v>
       </c>
@@ -2852,7 +2833,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="178">
       <c r="A178" t="s">
         <v>179</v>
       </c>
@@ -2860,7 +2841,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="179">
       <c r="A179" t="s">
         <v>180</v>
       </c>
@@ -2868,7 +2849,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="180">
       <c r="A180" t="s">
         <v>181</v>
       </c>
@@ -2876,7 +2857,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="181">
       <c r="A181" t="s">
         <v>182</v>
       </c>
@@ -2884,7 +2865,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="182">
       <c r="A182" t="s">
         <v>183</v>
       </c>
@@ -2892,7 +2873,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="183">
       <c r="A183" t="s">
         <v>184</v>
       </c>
@@ -2900,7 +2881,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="184">
       <c r="A184" t="s">
         <v>185</v>
       </c>
@@ -2908,7 +2889,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="185">
       <c r="A185" t="s">
         <v>186</v>
       </c>
@@ -2916,7 +2897,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="186">
       <c r="A186" t="s">
         <v>187</v>
       </c>
@@ -2924,7 +2905,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="187">
       <c r="A187" t="s">
         <v>188</v>
       </c>
@@ -2932,7 +2913,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="188">
       <c r="A188" t="s">
         <v>189</v>
       </c>
@@ -2940,7 +2921,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="189">
       <c r="A189" t="s">
         <v>190</v>
       </c>
@@ -2948,7 +2929,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="190">
       <c r="A190" t="s">
         <v>191</v>
       </c>
@@ -2956,7 +2937,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="191">
       <c r="A191" t="s">
         <v>192</v>
       </c>
@@ -2964,7 +2945,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="192">
       <c r="A192" t="s">
         <v>193</v>
       </c>
@@ -2972,7 +2953,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="193">
       <c r="A193" t="s">
         <v>194</v>
       </c>
@@ -2980,7 +2961,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="194">
       <c r="A194" t="s">
         <v>195</v>
       </c>
@@ -2988,7 +2969,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="195">
       <c r="A195" t="s">
         <v>196</v>
       </c>
@@ -2996,7 +2977,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="196">
       <c r="A196" t="s">
         <v>197</v>
       </c>
@@ -3004,7 +2985,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="197">
       <c r="A197" t="s">
         <v>198</v>
       </c>
@@ -3012,7 +2993,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="198">
       <c r="A198" t="s">
         <v>199</v>
       </c>
@@ -3020,7 +3001,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="199">
       <c r="A199" t="s">
         <v>200</v>
       </c>
@@ -3028,7 +3009,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="200">
       <c r="A200" t="s">
         <v>201</v>
       </c>
@@ -3036,7 +3017,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="201">
       <c r="A201" t="s">
         <v>202</v>
       </c>
@@ -3044,7 +3025,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="202">
       <c r="A202" t="s">
         <v>203</v>
       </c>
@@ -3052,7 +3033,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="203">
       <c r="A203" t="s">
         <v>204</v>
       </c>
@@ -3060,7 +3041,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="204">
       <c r="A204" t="s">
         <v>205</v>
       </c>
@@ -3068,7 +3049,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="205">
       <c r="A205" t="s">
         <v>206</v>
       </c>
@@ -3076,7 +3057,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="206">
       <c r="A206" t="s">
         <v>207</v>
       </c>
@@ -3084,7 +3065,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="207">
       <c r="A207" t="s">
         <v>208</v>
       </c>
@@ -3092,7 +3073,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="208">
       <c r="A208" t="s">
         <v>209</v>
       </c>
@@ -3100,7 +3081,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="209">
       <c r="A209" t="s">
         <v>210</v>
       </c>
@@ -3108,7 +3089,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="210">
       <c r="A210" t="s">
         <v>211</v>
       </c>
@@ -3116,7 +3097,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="211">
       <c r="A211" t="s">
         <v>212</v>
       </c>
@@ -3124,7 +3105,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="212">
       <c r="A212" t="s">
         <v>213</v>
       </c>
@@ -3132,7 +3113,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="213">
       <c r="A213" t="s">
         <v>214</v>
       </c>
@@ -3140,7 +3121,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="214">
       <c r="A214" t="s">
         <v>215</v>
       </c>
@@ -3148,7 +3129,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="215">
       <c r="A215" t="s">
         <v>216</v>
       </c>
@@ -3156,7 +3137,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="216">
       <c r="A216" t="s">
         <v>217</v>
       </c>
@@ -3164,7 +3145,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="217">
       <c r="A217" t="s">
         <v>218</v>
       </c>
@@ -3172,7 +3153,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="218">
       <c r="A218" t="s">
         <v>219</v>
       </c>
@@ -3180,7 +3161,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="219">
       <c r="A219" t="s">
         <v>220</v>
       </c>
@@ -3188,7 +3169,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="220">
       <c r="A220" t="s">
         <v>221</v>
       </c>
@@ -3196,7 +3177,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="221">
       <c r="A221" t="s">
         <v>222</v>
       </c>
@@ -3204,7 +3185,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="222">
       <c r="A222" t="s">
         <v>223</v>
       </c>
@@ -3212,7 +3193,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="223">
       <c r="A223" t="s">
         <v>224</v>
       </c>
@@ -3220,7 +3201,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="224">
       <c r="A224" t="s">
         <v>225</v>
       </c>
@@ -3228,7 +3209,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="225">
       <c r="A225" t="s">
         <v>226</v>
       </c>
@@ -3236,7 +3217,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="226">
       <c r="A226" t="s">
         <v>227</v>
       </c>
@@ -3244,7 +3225,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="227">
       <c r="A227" t="s">
         <v>228</v>
       </c>
@@ -3252,7 +3233,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="228">
       <c r="A228" t="s">
         <v>229</v>
       </c>
@@ -3260,7 +3241,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="229">
       <c r="A229" t="s">
         <v>230</v>
       </c>
@@ -3268,7 +3249,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="230">
       <c r="A230" t="s">
         <v>231</v>
       </c>
@@ -3276,7 +3257,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="231">
       <c r="A231" t="s">
         <v>232</v>
       </c>
@@ -3284,7 +3265,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="232">
       <c r="A232" t="s">
         <v>233</v>
       </c>
@@ -3292,7 +3273,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="233">
       <c r="A233" t="s">
         <v>234</v>
       </c>
@@ -3300,7 +3281,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="234">
       <c r="A234" t="s">
         <v>235</v>
       </c>
@@ -3308,7 +3289,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="235">
       <c r="A235" t="s">
         <v>236</v>
       </c>
@@ -3316,7 +3297,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="236">
       <c r="A236" t="s">
         <v>237</v>
       </c>
@@ -3324,7 +3305,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="237">
       <c r="A237" t="s">
         <v>238</v>
       </c>
@@ -3332,7 +3313,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="238">
       <c r="A238" t="s">
         <v>239</v>
       </c>
@@ -3340,7 +3321,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="239">
       <c r="A239" t="s">
         <v>240</v>
       </c>
@@ -3348,7 +3329,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="240">
       <c r="A240" t="s">
         <v>241</v>
       </c>
@@ -3356,7 +3337,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="241">
       <c r="A241" t="s">
         <v>242</v>
       </c>
@@ -3364,7 +3345,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="242">
       <c r="A242" t="s">
         <v>243</v>
       </c>
@@ -3372,7 +3353,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="243">
       <c r="A243" t="s">
         <v>244</v>
       </c>
@@ -3380,7 +3361,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="244">
       <c r="A244" t="s">
         <v>245</v>
       </c>
@@ -3388,7 +3369,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="245">
       <c r="A245" t="s">
         <v>246</v>
       </c>
@@ -3396,7 +3377,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="246">
       <c r="A246" t="s">
         <v>247</v>
       </c>
@@ -3404,7 +3385,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="247">
       <c r="A247" t="s">
         <v>248</v>
       </c>
@@ -3412,7 +3393,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="248">
       <c r="A248" t="s">
         <v>249</v>
       </c>
@@ -3420,7 +3401,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="249">
       <c r="A249" t="s">
         <v>250</v>
       </c>
@@ -3428,7 +3409,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="250">
       <c r="A250" t="s">
         <v>251</v>
       </c>
@@ -3436,7 +3417,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="251">
       <c r="A251" t="s">
         <v>252</v>
       </c>
@@ -3444,7 +3425,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="252">
       <c r="A252" t="s">
         <v>253</v>
       </c>
@@ -3452,7 +3433,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="253">
       <c r="A253" t="s">
         <v>254</v>
       </c>
@@ -3460,7 +3441,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="254">
       <c r="A254" t="s">
         <v>255</v>
       </c>
@@ -3468,7 +3449,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="255">
       <c r="A255" t="s">
         <v>256</v>
       </c>
@@ -3476,7 +3457,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="256">
       <c r="A256" t="s">
         <v>257</v>
       </c>
@@ -3484,7 +3465,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="257">
       <c r="A257" t="s">
         <v>258</v>
       </c>
@@ -3492,7 +3473,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="258">
       <c r="A258" t="s">
         <v>259</v>
       </c>
@@ -3500,7 +3481,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="259">
       <c r="A259" t="s">
         <v>260</v>
       </c>
@@ -3508,7 +3489,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="260">
       <c r="A260" t="s">
         <v>261</v>
       </c>
@@ -3516,7 +3497,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="261">
       <c r="A261" t="s">
         <v>262</v>
       </c>
@@ -3524,7 +3505,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="262">
       <c r="A262" t="s">
         <v>263</v>
       </c>
@@ -3532,7 +3513,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="263">
       <c r="A263" t="s">
         <v>264</v>
       </c>
@@ -3540,7 +3521,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="264">
       <c r="A264" t="s">
         <v>265</v>
       </c>
@@ -3548,7 +3529,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="265">
       <c r="A265" t="s">
         <v>266</v>
       </c>
@@ -3556,7 +3537,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="266">
       <c r="A266" t="s">
         <v>267</v>
       </c>
@@ -3564,7 +3545,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="267">
       <c r="A267" t="s">
         <v>268</v>
       </c>
@@ -3572,7 +3553,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="268">
       <c r="A268" t="s">
         <v>269</v>
       </c>
@@ -3580,7 +3561,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="269">
       <c r="A269" t="s">
         <v>270</v>
       </c>
@@ -3588,7 +3569,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="270">
       <c r="A270" t="s">
         <v>271</v>
       </c>
@@ -3596,7 +3577,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="271">
       <c r="A271" t="s">
         <v>272</v>
       </c>
@@ -3604,7 +3585,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="272">
       <c r="A272" t="s">
         <v>273</v>
       </c>
@@ -3612,7 +3593,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="273">
       <c r="A273" t="s">
         <v>274</v>
       </c>
@@ -3620,7 +3601,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="274">
       <c r="A274" t="s">
         <v>275</v>
       </c>
@@ -3628,7 +3609,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="275">
       <c r="A275" t="s">
         <v>276</v>
       </c>
@@ -3636,7 +3617,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="276">
       <c r="A276" t="s">
         <v>277</v>
       </c>
@@ -3644,7 +3625,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="277">
       <c r="A277" t="s">
         <v>278</v>
       </c>
@@ -3652,7 +3633,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="278">
       <c r="A278" t="s">
         <v>279</v>
       </c>
@@ -3660,7 +3641,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="279">
       <c r="A279" t="s">
         <v>280</v>
       </c>
@@ -3668,7 +3649,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="280">
       <c r="A280" t="s">
         <v>281</v>
       </c>
@@ -3676,7 +3657,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="281">
       <c r="A281" t="s">
         <v>282</v>
       </c>
@@ -3684,7 +3665,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="282">
       <c r="A282" t="s">
         <v>283</v>
       </c>
@@ -3692,7 +3673,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="283">
       <c r="A283" t="s">
         <v>284</v>
       </c>
@@ -3700,7 +3681,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="284">
       <c r="A284" t="s">
         <v>285</v>
       </c>
@@ -3708,7 +3689,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="285">
       <c r="A285" t="s">
         <v>286</v>
       </c>
@@ -3716,7 +3697,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="286">
       <c r="A286" t="s">
         <v>287</v>
       </c>
@@ -3724,7 +3705,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="287">
       <c r="A287" t="s">
         <v>288</v>
       </c>
@@ -3732,7 +3713,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="288">
       <c r="A288" t="s">
         <v>289</v>
       </c>
@@ -3740,7 +3721,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="289">
       <c r="A289" t="s">
         <v>290</v>
       </c>
@@ -3748,7 +3729,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="290">
       <c r="A290" t="s">
         <v>291</v>
       </c>
@@ -3756,7 +3737,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="291">
       <c r="A291" t="s">
         <v>292</v>
       </c>
@@ -3764,7 +3745,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="292">
       <c r="A292" t="s">
         <v>293</v>
       </c>
@@ -3772,7 +3753,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="293">
       <c r="A293" t="s">
         <v>294</v>
       </c>
@@ -3780,7 +3761,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="294">
       <c r="A294" t="s">
         <v>295</v>
       </c>
@@ -3788,7 +3769,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="295">
       <c r="A295" t="s">
         <v>296</v>
       </c>
@@ -3796,7 +3777,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="296">
       <c r="A296" t="s">
         <v>297</v>
       </c>
@@ -3804,7 +3785,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="297">
       <c r="A297" t="s">
         <v>298</v>
       </c>
@@ -3812,7 +3793,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="298">
       <c r="A298" t="s">
         <v>299</v>
       </c>
@@ -3820,7 +3801,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="299">
       <c r="A299" t="s">
         <v>300</v>
       </c>
@@ -3828,7 +3809,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="300">
       <c r="A300" t="s">
         <v>301</v>
       </c>
@@ -3836,7 +3817,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="301">
       <c r="A301" t="s">
         <v>302</v>
       </c>
@@ -3844,7 +3825,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="302">
       <c r="A302" t="s">
         <v>303</v>
       </c>
@@ -3852,7 +3833,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="303">
       <c r="A303" t="s">
         <v>304</v>
       </c>
@@ -3860,7 +3841,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="304">
       <c r="A304" t="s">
         <v>305</v>
       </c>
@@ -3868,7 +3849,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="305">
       <c r="A305" t="s">
         <v>306</v>
       </c>
@@ -3876,7 +3857,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="306">
       <c r="A306" t="s">
         <v>307</v>
       </c>
@@ -3884,7 +3865,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="307">
       <c r="A307" t="s">
         <v>308</v>
       </c>
@@ -3892,7 +3873,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="308">
       <c r="A308" t="s">
         <v>309</v>
       </c>
@@ -3900,7 +3881,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="309">
       <c r="A309" t="s">
         <v>310</v>
       </c>
@@ -3908,7 +3889,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="310">
       <c r="A310" t="s">
         <v>311</v>
       </c>
@@ -3916,7 +3897,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="311">
       <c r="A311" t="s">
         <v>312</v>
       </c>
@@ -3924,7 +3905,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="312">
       <c r="A312" t="s">
         <v>313</v>
       </c>
@@ -3932,7 +3913,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="313">
       <c r="A313" t="s">
         <v>314</v>
       </c>
@@ -3940,7 +3921,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="314">
       <c r="A314" t="s">
         <v>315</v>
       </c>
@@ -3948,7 +3929,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="315">
       <c r="A315" t="s">
         <v>316</v>
       </c>
@@ -3956,7 +3937,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="316" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="316">
       <c r="A316" t="s">
         <v>317</v>
       </c>
@@ -3964,7 +3945,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="317">
       <c r="A317" t="s">
         <v>318</v>
       </c>
@@ -3972,7 +3953,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="318">
       <c r="A318" t="s">
         <v>319</v>
       </c>
@@ -3980,7 +3961,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="319">
       <c r="A319" t="s">
         <v>320</v>
       </c>
@@ -3988,7 +3969,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="320">
       <c r="A320" t="s">
         <v>321</v>
       </c>
@@ -3996,7 +3977,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="321">
       <c r="A321" t="s">
         <v>322</v>
       </c>
@@ -4004,7 +3985,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="322">
       <c r="A322" t="s">
         <v>323</v>
       </c>
@@ -4012,7 +3993,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="323">
       <c r="A323" t="s">
         <v>324</v>
       </c>
@@ -4020,7 +4001,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="324">
       <c r="A324" t="s">
         <v>325</v>
       </c>
@@ -4028,7 +4009,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="325">
       <c r="A325" t="s">
         <v>326</v>
       </c>
@@ -4036,7 +4017,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="326">
       <c r="A326" t="s">
         <v>327</v>
       </c>
@@ -4044,7 +4025,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="327">
       <c r="A327" t="s">
         <v>328</v>
       </c>
@@ -4052,7 +4033,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="328">
       <c r="A328" t="s">
         <v>329</v>
       </c>
@@ -4060,7 +4041,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="329">
       <c r="A329" t="s">
         <v>330</v>
       </c>
@@ -4068,7 +4049,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="330">
       <c r="A330" t="s">
         <v>331</v>
       </c>
@@ -4076,7 +4057,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="331">
       <c r="A331" t="s">
         <v>332</v>
       </c>
@@ -4084,7 +4065,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="332">
       <c r="A332" t="s">
         <v>333</v>
       </c>
@@ -4092,7 +4073,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="333">
       <c r="A333" t="s">
         <v>334</v>
       </c>
@@ -4100,7 +4081,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="334">
       <c r="A334" t="s">
         <v>335</v>
       </c>
@@ -4108,7 +4089,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="335">
       <c r="A335" t="s">
         <v>336</v>
       </c>
@@ -4116,7 +4097,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="336">
       <c r="A336" t="s">
         <v>337</v>
       </c>
@@ -4124,7 +4105,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="337">
       <c r="A337" t="s">
         <v>338</v>
       </c>
@@ -4132,7 +4113,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="338">
       <c r="A338" t="s">
         <v>339</v>
       </c>
@@ -4140,7 +4121,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="339">
       <c r="A339" t="s">
         <v>340</v>
       </c>
@@ -4148,7 +4129,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="340">
       <c r="A340" t="s">
         <v>341</v>
       </c>
@@ -4156,7 +4137,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="341">
       <c r="A341" t="s">
         <v>342</v>
       </c>
@@ -4164,7 +4145,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="342">
       <c r="A342" t="s">
         <v>343</v>
       </c>
@@ -4172,7 +4153,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="343">
       <c r="A343" t="s">
         <v>344</v>
       </c>
@@ -4180,7 +4161,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="344">
       <c r="A344" t="s">
         <v>345</v>
       </c>
@@ -4188,7 +4169,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="345">
       <c r="A345" t="s">
         <v>346</v>
       </c>
@@ -4196,7 +4177,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="346">
       <c r="A346" t="s">
         <v>347</v>
       </c>
@@ -4206,16 +4187,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>348</v>
       </c>
@@ -4231,6 +4212,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>